--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/82.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/82.xlsx
@@ -426,13 +426,13 @@
         <v>-3.045951138531028</v>
       </c>
       <c r="E2">
-        <v>-9.233438711744334</v>
+        <v>-11.54804830233923</v>
       </c>
       <c r="F2">
-        <v>-3.08292102800058</v>
+        <v>-3.782142639234032</v>
       </c>
       <c r="G2">
-        <v>-9.536202260547935</v>
+        <v>-10.58064238257346</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.407938888811377</v>
       </c>
       <c r="E3">
-        <v>-9.779594307381938</v>
+        <v>-13.14759119271575</v>
       </c>
       <c r="F3">
-        <v>-3.669091197936969</v>
+        <v>-3.494947660683443</v>
       </c>
       <c r="G3">
-        <v>-9.915341116930882</v>
+        <v>-10.54518324953696</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.799535928832798</v>
       </c>
       <c r="E4">
-        <v>-11.39763975421056</v>
+        <v>-13.17725342799767</v>
       </c>
       <c r="F4">
-        <v>-3.277569971943005</v>
+        <v>-3.375424184868308</v>
       </c>
       <c r="G4">
-        <v>-9.747591639345785</v>
+        <v>-10.00336106544797</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.146967575042147</v>
       </c>
       <c r="E5">
-        <v>-11.19464324428692</v>
+        <v>-13.3248294860028</v>
       </c>
       <c r="F5">
-        <v>-2.982440062041</v>
+        <v>-3.501823110126679</v>
       </c>
       <c r="G5">
-        <v>-9.632883354246042</v>
+        <v>-9.812165796062382</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.429696097632195</v>
       </c>
       <c r="E6">
-        <v>-11.82728946576408</v>
+        <v>-14.89404562728542</v>
       </c>
       <c r="F6">
-        <v>-3.387324510976926</v>
+        <v>-3.801634124221904</v>
       </c>
       <c r="G6">
-        <v>-9.749612355659307</v>
+        <v>-9.538995757260425</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.607666613966422</v>
       </c>
       <c r="E7">
-        <v>-13.57008492115658</v>
+        <v>-15.63478747991389</v>
       </c>
       <c r="F7">
-        <v>-3.451943795334509</v>
+        <v>-3.168753973176456</v>
       </c>
       <c r="G7">
-        <v>-8.405839923284274</v>
+        <v>-9.441500111249891</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.653945967146875</v>
       </c>
       <c r="E8">
-        <v>-13.65212745766724</v>
+        <v>-15.73724720329741</v>
       </c>
       <c r="F8">
-        <v>-3.589864482798419</v>
+        <v>-3.205684248728064</v>
       </c>
       <c r="G8">
-        <v>-8.238044757668833</v>
+        <v>-9.160302032830261</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.531698030836264</v>
       </c>
       <c r="E9">
-        <v>-13.46561919670317</v>
+        <v>-16.87365719241965</v>
       </c>
       <c r="F9">
-        <v>-2.67820970785184</v>
+        <v>-3.616545368475188</v>
       </c>
       <c r="G9">
-        <v>-7.905609511276309</v>
+        <v>-8.858062658378554</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.218625201672806</v>
       </c>
       <c r="E10">
-        <v>-14.69742429674539</v>
+        <v>-18.5303981091617</v>
       </c>
       <c r="F10">
-        <v>-2.823839182366201</v>
+        <v>-3.580525468699257</v>
       </c>
       <c r="G10">
-        <v>-8.105002518677995</v>
+        <v>-7.843323672193824</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.694976557637474</v>
       </c>
       <c r="E11">
-        <v>-14.19908046987921</v>
+        <v>-18.71685653158988</v>
       </c>
       <c r="F11">
-        <v>-2.534395186317012</v>
+        <v>-3.238753503815223</v>
       </c>
       <c r="G11">
-        <v>-6.944453447079589</v>
+        <v>-6.844662956573465</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.973126575573585</v>
       </c>
       <c r="E12">
-        <v>-18.05640456029299</v>
+        <v>-19.48731045803617</v>
       </c>
       <c r="F12">
-        <v>-3.100854353903787</v>
+        <v>-3.608839066526945</v>
       </c>
       <c r="G12">
-        <v>-4.863951082421411</v>
+        <v>-6.483098327405595</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.082810823501544</v>
       </c>
       <c r="E13">
-        <v>-18.56766072116806</v>
+        <v>-20.62145279377505</v>
       </c>
       <c r="F13">
-        <v>-3.172279504842771</v>
+        <v>-3.142833528775457</v>
       </c>
       <c r="G13">
-        <v>-6.171790531616656</v>
+        <v>-6.558914350331525</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.092033404813681</v>
       </c>
       <c r="E14">
-        <v>-18.18463495994708</v>
+        <v>-21.79764224096649</v>
       </c>
       <c r="F14">
-        <v>-2.66578502517725</v>
+        <v>-3.898259039921452</v>
       </c>
       <c r="G14">
-        <v>-4.098065659917009</v>
+        <v>-5.104510310535772</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.07315712326740102</v>
       </c>
       <c r="E15">
-        <v>-20.40664455084359</v>
+        <v>-22.93937249379583</v>
       </c>
       <c r="F15">
-        <v>-2.829310549061692</v>
+        <v>-3.574340049302553</v>
       </c>
       <c r="G15">
-        <v>-4.529971580603244</v>
+        <v>-4.328886810706517</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.8927370475268368</v>
       </c>
       <c r="E16">
-        <v>-20.5790734254165</v>
+        <v>-24.35934713933206</v>
       </c>
       <c r="F16">
-        <v>-3.107158229839091</v>
+        <v>-3.679633001504996</v>
       </c>
       <c r="G16">
-        <v>-3.504183923308923</v>
+        <v>-4.248026829230556</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.750930640242162</v>
       </c>
       <c r="E17">
-        <v>-20.79038881762377</v>
+        <v>-24.17084533693207</v>
       </c>
       <c r="F17">
-        <v>-3.509248595525374</v>
+        <v>-3.432416690548317</v>
       </c>
       <c r="G17">
-        <v>-3.425415148250444</v>
+        <v>-3.40591810764401</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.46398120216913</v>
       </c>
       <c r="E18">
-        <v>-21.8507701202337</v>
+        <v>-25.80263376003455</v>
       </c>
       <c r="F18">
-        <v>-2.870338758154949</v>
+        <v>-3.414030247675779</v>
       </c>
       <c r="G18">
-        <v>-2.908088275287573</v>
+        <v>-2.865274674737906</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.022674732482507</v>
       </c>
       <c r="E19">
-        <v>-24.19723899490135</v>
+        <v>-26.88836211135991</v>
       </c>
       <c r="F19">
-        <v>-2.341505694738133</v>
+        <v>-3.903284744954237</v>
       </c>
       <c r="G19">
-        <v>-1.946605868016963</v>
+        <v>-2.732066653465533</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.42720559211649</v>
       </c>
       <c r="E20">
-        <v>-24.34346941243724</v>
+        <v>-27.18982295537258</v>
       </c>
       <c r="F20">
-        <v>-2.490552184789042</v>
+        <v>-3.462639675239457</v>
       </c>
       <c r="G20">
-        <v>-2.507289376404453</v>
+        <v>-1.721019260132638</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.689583596731815</v>
       </c>
       <c r="E21">
-        <v>-25.30764572791884</v>
+        <v>-28.26285078646661</v>
       </c>
       <c r="F21">
-        <v>-2.157658661728214</v>
+        <v>-3.006408044473601</v>
       </c>
       <c r="G21">
-        <v>-1.468040719998351</v>
+        <v>-2.109216094874454</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.825150455842046</v>
       </c>
       <c r="E22">
-        <v>-26.11468944613687</v>
+        <v>-28.3187696237441</v>
       </c>
       <c r="F22">
-        <v>-2.340314502412908</v>
+        <v>-3.188725911257952</v>
       </c>
       <c r="G22">
-        <v>-1.406860531250203</v>
+        <v>-1.37012996559783</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.852479190221596</v>
       </c>
       <c r="E23">
-        <v>-25.85030847283226</v>
+        <v>-28.73590155636458</v>
       </c>
       <c r="F23">
-        <v>-1.899619730653959</v>
+        <v>-2.759111381878851</v>
       </c>
       <c r="G23">
-        <v>-1.811797460310238</v>
+        <v>-1.650510880960441</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.790364494051206</v>
       </c>
       <c r="E24">
-        <v>-26.66650171559889</v>
+        <v>-30.06003669736907</v>
       </c>
       <c r="F24">
-        <v>-1.922139726866467</v>
+        <v>-2.898195925543693</v>
       </c>
       <c r="G24">
-        <v>-1.612952709272685</v>
+        <v>-0.9106911324537138</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.655549255938508</v>
       </c>
       <c r="E25">
-        <v>-28.82003315817164</v>
+        <v>-30.61072967637905</v>
       </c>
       <c r="F25">
-        <v>-2.304244072225406</v>
+        <v>-2.930700234062143</v>
       </c>
       <c r="G25">
-        <v>-1.567296007863296</v>
+        <v>-0.920559747008122</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.461648883820828</v>
       </c>
       <c r="E26">
-        <v>-25.30283215599336</v>
+        <v>-30.52316959862335</v>
       </c>
       <c r="F26">
-        <v>-2.262223478983595</v>
+        <v>-2.968731409892071</v>
       </c>
       <c r="G26">
-        <v>-1.01309236755095</v>
+        <v>-1.551550607234292</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.218378679244595</v>
       </c>
       <c r="E27">
-        <v>-28.50306837628337</v>
+        <v>-29.84415277270448</v>
       </c>
       <c r="F27">
-        <v>-1.636048133696407</v>
+        <v>-2.753673149879472</v>
       </c>
       <c r="G27">
-        <v>-1.922495641718032</v>
+        <v>-2.102973804557103</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.929859179024755</v>
       </c>
       <c r="E28">
-        <v>-27.12933973884911</v>
+        <v>-31.12007328343903</v>
       </c>
       <c r="F28">
-        <v>-1.483569717495699</v>
+        <v>-2.549038236896299</v>
       </c>
       <c r="G28">
-        <v>-1.947926904780067</v>
+        <v>-1.744774425167178</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.600273815430398</v>
       </c>
       <c r="E29">
-        <v>-27.9615851433862</v>
+        <v>-30.53831013050801</v>
       </c>
       <c r="F29">
-        <v>-1.210132264770805</v>
+        <v>-2.683613976787704</v>
       </c>
       <c r="G29">
-        <v>-0.9501864766280756</v>
+        <v>-1.70345939201281</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.228734744756622</v>
       </c>
       <c r="E30">
-        <v>-27.27397117002494</v>
+        <v>-29.79851105685028</v>
       </c>
       <c r="F30">
-        <v>-2.549611467139036</v>
+        <v>-2.771258561473503</v>
       </c>
       <c r="G30">
-        <v>-1.42524017317164</v>
+        <v>-2.15488846075139</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.821597596066601</v>
       </c>
       <c r="E31">
-        <v>-26.97334512148855</v>
+        <v>-30.39959287225874</v>
       </c>
       <c r="F31">
-        <v>-1.963541529658386</v>
+        <v>-2.628362699388379</v>
       </c>
       <c r="G31">
-        <v>-2.912398614607501</v>
+        <v>-2.635388170512017</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.381396128696038</v>
       </c>
       <c r="E32">
-        <v>-26.808554002542</v>
+        <v>-29.38584590300965</v>
       </c>
       <c r="F32">
-        <v>-2.218456687256683</v>
+        <v>-2.55313368533574</v>
       </c>
       <c r="G32">
-        <v>-2.928311102890337</v>
+        <v>-2.597824777335079</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.9226824718328676</v>
       </c>
       <c r="E33">
-        <v>-26.02578580451759</v>
+        <v>-29.37830990106075</v>
       </c>
       <c r="F33">
-        <v>-2.136443344175115</v>
+        <v>-2.435954489270527</v>
       </c>
       <c r="G33">
-        <v>-2.679862204621632</v>
+        <v>-3.192951839113126</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.453717562281914</v>
       </c>
       <c r="E34">
-        <v>-25.07039353098801</v>
+        <v>-29.01776962595239</v>
       </c>
       <c r="F34">
-        <v>-1.456226966264093</v>
+        <v>-2.528220535696545</v>
       </c>
       <c r="G34">
-        <v>-3.094738238340035</v>
+        <v>-3.246056994840961</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.006543604055099557</v>
       </c>
       <c r="E35">
-        <v>-25.03315583824959</v>
+        <v>-28.57695400575207</v>
       </c>
       <c r="F35">
-        <v>-1.423400422825954</v>
+        <v>-2.273045270733768</v>
       </c>
       <c r="G35">
-        <v>-2.248888319754424</v>
+        <v>-2.860081903746182</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.4481535943300892</v>
       </c>
       <c r="E36">
-        <v>-26.07669586893734</v>
+        <v>-27.3687100735556</v>
       </c>
       <c r="F36">
-        <v>-1.715782638052873</v>
+        <v>-2.40791590942057</v>
       </c>
       <c r="G36">
-        <v>-2.782041526428624</v>
+        <v>-3.285549728270732</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.8552985058254874</v>
       </c>
       <c r="E37">
-        <v>-23.60131962116965</v>
+        <v>-27.87339585411479</v>
       </c>
       <c r="F37">
-        <v>-1.28976570830413</v>
+        <v>-2.23184227611852</v>
       </c>
       <c r="G37">
-        <v>-2.702996012443487</v>
+        <v>-3.545290096896001</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.222518860313548</v>
       </c>
       <c r="E38">
-        <v>-22.58843444327047</v>
+        <v>-25.6846617923528</v>
       </c>
       <c r="F38">
-        <v>-1.419003448651895</v>
+        <v>-2.34972475610871</v>
       </c>
       <c r="G38">
-        <v>-2.737541384873098</v>
+        <v>-3.608942660771935</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.542314256605084</v>
       </c>
       <c r="E39">
-        <v>-23.67430400378087</v>
+        <v>-25.73888196619843</v>
       </c>
       <c r="F39">
-        <v>-1.628205151126701</v>
+        <v>-2.081560690270037</v>
       </c>
       <c r="G39">
-        <v>-3.377630689999298</v>
+        <v>-3.831547798333209</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.816570421430345</v>
       </c>
       <c r="E40">
-        <v>-21.86060077143957</v>
+        <v>-25.67225199691421</v>
       </c>
       <c r="F40">
-        <v>-1.442753570457559</v>
+        <v>-1.715017226572687</v>
       </c>
       <c r="G40">
-        <v>-3.165369322508014</v>
+        <v>-4.68323534182455</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.047224640491676</v>
       </c>
       <c r="E41">
-        <v>-20.7880339468026</v>
+        <v>-24.79596593948864</v>
       </c>
       <c r="F41">
-        <v>-1.156003425202274</v>
+        <v>-1.744726623474091</v>
       </c>
       <c r="G41">
-        <v>-3.342719813326931</v>
+        <v>-4.308188827588171</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.244937622675172</v>
       </c>
       <c r="E42">
-        <v>-21.50784361435393</v>
+        <v>-23.76927548714572</v>
       </c>
       <c r="F42">
-        <v>-1.322288240905441</v>
+        <v>-1.725167212359189</v>
       </c>
       <c r="G42">
-        <v>-3.5141204172227</v>
+        <v>-4.271186744498322</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.421699170020639</v>
       </c>
       <c r="E43">
-        <v>-20.56482791057234</v>
+        <v>-23.59511057023904</v>
       </c>
       <c r="F43">
-        <v>-0.6598593962347323</v>
+        <v>-1.559537635271636</v>
       </c>
       <c r="G43">
-        <v>-3.605060483564949</v>
+        <v>-4.410161900572464</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.595091671696104</v>
       </c>
       <c r="E44">
-        <v>-19.1286931197712</v>
+        <v>-22.39861607288051</v>
       </c>
       <c r="F44">
-        <v>-1.627985633764959</v>
+        <v>-1.306869838437134</v>
       </c>
       <c r="G44">
-        <v>-3.890088524299742</v>
+        <v>-4.993109838832968</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.782696138769659</v>
       </c>
       <c r="E45">
-        <v>-18.42172518163624</v>
+        <v>-21.3559855954729</v>
       </c>
       <c r="F45">
-        <v>-1.539297306151633</v>
+        <v>-1.452972310738494</v>
       </c>
       <c r="G45">
-        <v>-3.310699030916926</v>
+        <v>-5.030365164148154</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.002671676553515</v>
       </c>
       <c r="E46">
-        <v>-17.25846468129899</v>
+        <v>-20.35520287537427</v>
       </c>
       <c r="F46">
-        <v>-1.601314688497024</v>
+        <v>-1.610102838273324</v>
       </c>
       <c r="G46">
-        <v>-4.091512690993315</v>
+        <v>-5.234324363839697</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.271387256288976</v>
       </c>
       <c r="E47">
-        <v>-17.50987517563616</v>
+        <v>-20.05692339123641</v>
       </c>
       <c r="F47">
-        <v>-0.8600989917786512</v>
+        <v>-1.560522564113565</v>
       </c>
       <c r="G47">
-        <v>-3.648367514842336</v>
+        <v>-5.777865723241937</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.599729058337346</v>
       </c>
       <c r="E48">
-        <v>-16.55051243208004</v>
+        <v>-19.17473562051825</v>
       </c>
       <c r="F48">
-        <v>-1.019061039641071</v>
+        <v>-1.374120017666009</v>
       </c>
       <c r="G48">
-        <v>-5.809575827045599</v>
+        <v>-5.865341331511779</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.996735660140912</v>
       </c>
       <c r="E49">
-        <v>-15.73141609459735</v>
+        <v>-18.27246707304455</v>
       </c>
       <c r="F49">
-        <v>-0.6764607073542372</v>
+        <v>-1.594106235357862</v>
       </c>
       <c r="G49">
-        <v>-3.724120879898079</v>
+        <v>-6.495141692204401</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.461346104097622</v>
       </c>
       <c r="E50">
-        <v>-14.33717889964108</v>
+        <v>-16.48632039784349</v>
       </c>
       <c r="F50">
-        <v>-0.9411464584685548</v>
+        <v>-1.12346846708992</v>
       </c>
       <c r="G50">
-        <v>-4.140806159618124</v>
+        <v>-6.596057413629294</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.99231172400385</v>
       </c>
       <c r="E51">
-        <v>-14.98777114725283</v>
+        <v>-16.97724658928352</v>
       </c>
       <c r="F51">
-        <v>-0.8737687106596487</v>
+        <v>-1.378379482851204</v>
       </c>
       <c r="G51">
-        <v>-5.388507107157075</v>
+        <v>-6.863538639967214</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.574201870830332</v>
       </c>
       <c r="E52">
-        <v>-13.42635058362691</v>
+        <v>-16.1117422684572</v>
       </c>
       <c r="F52">
-        <v>-1.32043269792317</v>
+        <v>-1.398300062153726</v>
       </c>
       <c r="G52">
-        <v>-5.062338953155519</v>
+        <v>-6.274847063606262</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.196099374996557</v>
       </c>
       <c r="E53">
-        <v>-14.91650204091877</v>
+        <v>-15.92976516104851</v>
       </c>
       <c r="F53">
-        <v>-1.244937777934232</v>
+        <v>-1.227981097198926</v>
       </c>
       <c r="G53">
-        <v>-5.238167379877816</v>
+        <v>-6.615789421248929</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.831363245497065</v>
       </c>
       <c r="E54">
-        <v>-12.06812173085691</v>
+        <v>-13.82345988445039</v>
       </c>
       <c r="F54">
-        <v>-1.849418180942101</v>
+        <v>-1.447539048943532</v>
       </c>
       <c r="G54">
-        <v>-6.533861645235202</v>
+        <v>-6.672330316858669</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.463275828713829</v>
       </c>
       <c r="E55">
-        <v>-11.32655754238612</v>
+        <v>-13.54754959650806</v>
       </c>
       <c r="F55">
-        <v>-1.399219549970834</v>
+        <v>-1.068024180085744</v>
       </c>
       <c r="G55">
-        <v>-6.298213227696726</v>
+        <v>-7.844102979454271</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.0620175497644</v>
       </c>
       <c r="E56">
-        <v>-11.46478056848774</v>
+        <v>-12.85785901748438</v>
       </c>
       <c r="F56">
-        <v>-1.529430622016888</v>
+        <v>-1.208567478746917</v>
       </c>
       <c r="G56">
-        <v>-5.094456333115394</v>
+        <v>-7.732673789560965</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.611745032745338</v>
       </c>
       <c r="E57">
-        <v>-11.4112456745107</v>
+        <v>-12.66207663563196</v>
       </c>
       <c r="F57">
-        <v>-1.013314654967851</v>
+        <v>-1.485759092541298</v>
       </c>
       <c r="G57">
-        <v>-5.754371632666508</v>
+        <v>-7.294987680350005</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.08928380083997</v>
       </c>
       <c r="E58">
-        <v>-11.69398384187106</v>
+        <v>-12.19797188292767</v>
       </c>
       <c r="F58">
-        <v>-0.6340955132728621</v>
+        <v>-1.529044602807184</v>
       </c>
       <c r="G58">
-        <v>-7.555691413729395</v>
+        <v>-7.689097851590693</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.486826003514848</v>
       </c>
       <c r="E59">
-        <v>-10.21850983340114</v>
+        <v>-11.77068534861799</v>
       </c>
       <c r="F59">
-        <v>-0.9429580979784774</v>
+        <v>-1.346633958873718</v>
       </c>
       <c r="G59">
-        <v>-7.172977142628917</v>
+        <v>-7.983997117624486</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.792754857458419</v>
       </c>
       <c r="E60">
-        <v>-8.39520437647684</v>
+        <v>-11.34002640671254</v>
       </c>
       <c r="F60">
-        <v>-0.7423747299623967</v>
+        <v>-1.359317920545384</v>
       </c>
       <c r="G60">
-        <v>-6.335264914933806</v>
+        <v>-7.97243543520274</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.01059265358019</v>
       </c>
       <c r="E61">
-        <v>-8.882538040120895</v>
+        <v>-9.97222440183881</v>
       </c>
       <c r="F61">
-        <v>-1.587620118593942</v>
+        <v>-1.820122967742096</v>
       </c>
       <c r="G61">
-        <v>-7.327533222422823</v>
+        <v>-7.887992206775476</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.14143413661525</v>
       </c>
       <c r="E62">
-        <v>-9.858933103320137</v>
+        <v>-9.701052928018106</v>
       </c>
       <c r="F62">
-        <v>-1.783731959369711</v>
+        <v>-1.099927093869761</v>
       </c>
       <c r="G62">
-        <v>-6.580398167571796</v>
+        <v>-8.228975030959305</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.19866813635386</v>
       </c>
       <c r="E63">
-        <v>-9.024316215116569</v>
+        <v>-9.667582197951312</v>
       </c>
       <c r="F63">
-        <v>-0.8833148166095102</v>
+        <v>-1.679307136205403</v>
       </c>
       <c r="G63">
-        <v>-6.136234801030284</v>
+        <v>-8.433828410673305</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.19103582305678</v>
       </c>
       <c r="E64">
-        <v>-7.948248233332767</v>
+        <v>-10.12624624382008</v>
       </c>
       <c r="F64">
-        <v>-1.772296347374064</v>
+        <v>-1.336078073059844</v>
       </c>
       <c r="G64">
-        <v>-6.976651760121789</v>
+        <v>-7.949540510510972</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.13506693374188</v>
       </c>
       <c r="E65">
-        <v>-7.727750090886294</v>
+        <v>-8.863856895581817</v>
       </c>
       <c r="F65">
-        <v>-1.45121368674235</v>
+        <v>-1.491164189844565</v>
       </c>
       <c r="G65">
-        <v>-6.571179628420575</v>
+        <v>-8.726067327968753</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.04005348866679</v>
       </c>
       <c r="E66">
-        <v>-7.689586232022445</v>
+        <v>-9.33297042114385</v>
       </c>
       <c r="F66">
-        <v>-2.179931804454687</v>
+        <v>-1.784821262504392</v>
       </c>
       <c r="G66">
-        <v>-6.639270458101401</v>
+        <v>-8.712350475887042</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.920761207189411</v>
       </c>
       <c r="E67">
-        <v>-8.274981368257029</v>
+        <v>-8.39145402665052</v>
       </c>
       <c r="F67">
-        <v>-1.492970030782668</v>
+        <v>-1.553201453007623</v>
       </c>
       <c r="G67">
-        <v>-7.24835456046354</v>
+        <v>-8.78963373727318</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.784117233564841</v>
       </c>
       <c r="E68">
-        <v>-7.113494289155478</v>
+        <v>-8.775758976959555</v>
       </c>
       <c r="F68">
-        <v>-1.964303627668961</v>
+        <v>-1.859248416911123</v>
       </c>
       <c r="G68">
-        <v>-6.716652927781999</v>
+        <v>-9.047604021065673</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.641935598635609</v>
       </c>
       <c r="E69">
-        <v>-8.093988571932325</v>
+        <v>-7.665796637553827</v>
       </c>
       <c r="F69">
-        <v>-1.40638492800505</v>
+        <v>-1.766387602689895</v>
       </c>
       <c r="G69">
-        <v>-7.549770244996751</v>
+        <v>-8.70940163987138</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.497879567175383</v>
       </c>
       <c r="E70">
-        <v>-5.632766468359657</v>
+        <v>-7.778826283759036</v>
       </c>
       <c r="F70">
-        <v>-1.549777810531852</v>
+        <v>-1.58478461697416</v>
       </c>
       <c r="G70">
-        <v>-6.536723021307062</v>
+        <v>-8.388974513225683</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.360162037399146</v>
       </c>
       <c r="E71">
-        <v>-7.96027593332947</v>
+        <v>-7.10776701073854</v>
       </c>
       <c r="F71">
-        <v>-1.005260438710431</v>
+        <v>-1.925444912803637</v>
       </c>
       <c r="G71">
-        <v>-7.03345373019064</v>
+        <v>-8.315254918206417</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.229826318956922</v>
       </c>
       <c r="E72">
-        <v>-7.463186376283391</v>
+        <v>-7.63277860752144</v>
       </c>
       <c r="F72">
-        <v>-2.174720545123675</v>
+        <v>-2.085142550919742</v>
       </c>
       <c r="G72">
-        <v>-7.469792695192586</v>
+        <v>-8.238807095089438</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.11150083994848</v>
       </c>
       <c r="E73">
-        <v>-8.492975124274629</v>
+        <v>-7.587969610537865</v>
       </c>
       <c r="F73">
-        <v>-1.311559226304382</v>
+        <v>-2.003954261771363</v>
       </c>
       <c r="G73">
-        <v>-7.136178697617175</v>
+        <v>-8.18301156706046</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.00446582756223</v>
       </c>
       <c r="E74">
-        <v>-6.881512517395855</v>
+        <v>-8.118787396752877</v>
       </c>
       <c r="F74">
-        <v>-2.278601130904344</v>
+        <v>-1.93545904633608</v>
       </c>
       <c r="G74">
-        <v>-5.980023509165612</v>
+        <v>-7.676905674350194</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.909524371345331</v>
       </c>
       <c r="E75">
-        <v>-9.162319121017971</v>
+        <v>-8.513176344158595</v>
       </c>
       <c r="F75">
-        <v>-2.150670554318197</v>
+        <v>-1.723277706313403</v>
       </c>
       <c r="G75">
-        <v>-6.761450694220912</v>
+        <v>-7.152059856964917</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.825082098535095</v>
       </c>
       <c r="E76">
-        <v>-9.540950784657289</v>
+        <v>-8.13562451546373</v>
       </c>
       <c r="F76">
-        <v>-2.633408285238831</v>
+        <v>-2.039837480925832</v>
       </c>
       <c r="G76">
-        <v>-6.204539711767581</v>
+        <v>-7.661656315193501</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.748091477975009</v>
       </c>
       <c r="E77">
-        <v>-6.263834469533379</v>
+        <v>-8.962844534297782</v>
       </c>
       <c r="F77">
-        <v>-1.983287323438918</v>
+        <v>-1.919425995254895</v>
       </c>
       <c r="G77">
-        <v>-5.154200612338431</v>
+        <v>-7.214717727151636</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.676596458881296</v>
       </c>
       <c r="E78">
-        <v>-9.115882065195063</v>
+        <v>-9.413326753856634</v>
       </c>
       <c r="F78">
-        <v>-2.460243049888011</v>
+        <v>-2.130256268043606</v>
       </c>
       <c r="G78">
-        <v>-5.408784760396252</v>
+        <v>-6.987361034434535</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.605143018512843</v>
       </c>
       <c r="E79">
-        <v>-10.09041233650946</v>
+        <v>-9.400443492327016</v>
       </c>
       <c r="F79">
-        <v>-2.794268951188467</v>
+        <v>-2.219855799800012</v>
       </c>
       <c r="G79">
-        <v>-4.743697575810142</v>
+        <v>-6.526598553782725</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.532018389337477</v>
       </c>
       <c r="E80">
-        <v>-8.947340596422196</v>
+        <v>-10.11299334648255</v>
       </c>
       <c r="F80">
-        <v>-2.788391684465605</v>
+        <v>-1.866808097829071</v>
       </c>
       <c r="G80">
-        <v>-5.617404139182932</v>
+        <v>-6.327672869662848</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.450398838274912</v>
       </c>
       <c r="E81">
-        <v>-11.01061445048377</v>
+        <v>-10.52900391204532</v>
       </c>
       <c r="F81">
-        <v>-2.628850607788628</v>
+        <v>-1.868602341623534</v>
       </c>
       <c r="G81">
-        <v>-5.366608181526817</v>
+        <v>-6.735849732760455</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.359165433334688</v>
       </c>
       <c r="E82">
-        <v>-9.930733820703773</v>
+        <v>-10.53673719153216</v>
       </c>
       <c r="F82">
-        <v>-2.859066334537653</v>
+        <v>-1.884482144735201</v>
       </c>
       <c r="G82">
-        <v>-4.169981230423815</v>
+        <v>-5.850303442666966</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.250957776937309</v>
       </c>
       <c r="E83">
-        <v>-11.21847021765746</v>
+        <v>-11.31857091700848</v>
       </c>
       <c r="F83">
-        <v>-2.439274585820947</v>
+        <v>-2.082286340114889</v>
       </c>
       <c r="G83">
-        <v>-4.793262561872428</v>
+        <v>-6.034849145578991</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.126136004983106</v>
       </c>
       <c r="E84">
-        <v>-12.3428026682471</v>
+        <v>-12.20851273327009</v>
       </c>
       <c r="F84">
-        <v>-2.063376369043782</v>
+        <v>-2.302272557806743</v>
       </c>
       <c r="G84">
-        <v>-4.477654869741925</v>
+        <v>-5.565612187984427</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.979285182691529</v>
       </c>
       <c r="E85">
-        <v>-14.22041966966618</v>
+        <v>-13.39003075059129</v>
       </c>
       <c r="F85">
-        <v>-2.20655470441326</v>
+        <v>-2.035662509215722</v>
       </c>
       <c r="G85">
-        <v>-4.723417311826374</v>
+        <v>-5.082530451823189</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.81380580059026</v>
       </c>
       <c r="E86">
-        <v>-16.76797457704806</v>
+        <v>-14.48794047073236</v>
       </c>
       <c r="F86">
-        <v>-2.622684240842189</v>
+        <v>-2.093113102069479</v>
       </c>
       <c r="G86">
-        <v>-4.722756793444822</v>
+        <v>-4.363351250053803</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.628160947962524</v>
       </c>
       <c r="E87">
-        <v>-14.76893844254761</v>
+        <v>-15.36563862000838</v>
       </c>
       <c r="F87">
-        <v>-1.943396462789705</v>
+        <v>-2.391673281386477</v>
       </c>
       <c r="G87">
-        <v>-4.40452269225566</v>
+        <v>-4.525682127240045</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.43121079787914</v>
       </c>
       <c r="E88">
-        <v>-19.29063928896024</v>
+        <v>-16.5829739317949</v>
       </c>
       <c r="F88">
-        <v>-2.405071295759356</v>
+        <v>-2.506602631585686</v>
       </c>
       <c r="G88">
-        <v>-3.038280886557211</v>
+        <v>-4.86730066773181</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.228129534744335</v>
       </c>
       <c r="E89">
-        <v>-19.35975703182804</v>
+        <v>-17.53880644572491</v>
       </c>
       <c r="F89">
-        <v>-1.798626833639449</v>
+        <v>-2.525729634916326</v>
       </c>
       <c r="G89">
-        <v>-4.178970024051019</v>
+        <v>-4.888356322859138</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.033527491812492</v>
       </c>
       <c r="E90">
-        <v>-19.59735809851015</v>
+        <v>-19.46783605013405</v>
       </c>
       <c r="F90">
-        <v>-2.337316640782176</v>
+        <v>-2.202487420465514</v>
       </c>
       <c r="G90">
-        <v>-3.856083576000492</v>
+        <v>-4.675486651878125</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.856282858930276</v>
       </c>
       <c r="E91">
-        <v>-20.58795714444031</v>
+        <v>-20.45411575628638</v>
       </c>
       <c r="F91">
-        <v>-2.32268850081614</v>
+        <v>-2.300380566658749</v>
       </c>
       <c r="G91">
-        <v>-3.308853234491009</v>
+        <v>-5.148725880930866</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.709657716932778</v>
       </c>
       <c r="E92">
-        <v>-23.61981387119912</v>
+        <v>-22.46532079996858</v>
       </c>
       <c r="F92">
-        <v>-2.343081249538258</v>
+        <v>-2.234985102044742</v>
       </c>
       <c r="G92">
-        <v>-3.896730258539534</v>
+        <v>-4.963266417411952</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.599164693708659</v>
       </c>
       <c r="E93">
-        <v>-26.19846802498131</v>
+        <v>-24.41204723783281</v>
       </c>
       <c r="F93">
-        <v>-1.958082588473937</v>
+        <v>-2.221210180503589</v>
       </c>
       <c r="G93">
-        <v>-3.831067421328444</v>
+        <v>-5.249678152780034</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.529690348459068</v>
       </c>
       <c r="E94">
-        <v>-28.3414004722531</v>
+        <v>-26.1726890422881</v>
       </c>
       <c r="F94">
-        <v>-2.316829458176139</v>
+        <v>-2.306344811958905</v>
       </c>
       <c r="G94">
-        <v>-3.582367891578992</v>
+        <v>-5.186803590792254</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.50011446570398</v>
       </c>
       <c r="E95">
-        <v>-29.13169221259243</v>
+        <v>-27.62328116171097</v>
       </c>
       <c r="F95">
-        <v>-1.624531341695285</v>
+        <v>-2.520668310085221</v>
       </c>
       <c r="G95">
-        <v>-3.795026092248125</v>
+        <v>-5.344646598026372</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.505251044289756</v>
       </c>
       <c r="E96">
-        <v>-30.55071161952395</v>
+        <v>-30.463602165197</v>
       </c>
       <c r="F96">
-        <v>-3.060579130779675</v>
+        <v>-2.074439215708169</v>
       </c>
       <c r="G96">
-        <v>-3.994852483251936</v>
+        <v>-5.85303167076468</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.538330939344532</v>
       </c>
       <c r="E97">
-        <v>-34.51884961790115</v>
+        <v>-31.88436384427928</v>
       </c>
       <c r="F97">
-        <v>-2.491175117075948</v>
+        <v>-2.70640899097794</v>
       </c>
       <c r="G97">
-        <v>-4.999686304457982</v>
+        <v>-5.549433403753298</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.585333220229836</v>
       </c>
       <c r="E98">
-        <v>-36.27922146362032</v>
+        <v>-33.74094067712679</v>
       </c>
       <c r="F98">
-        <v>-2.352401211187155</v>
+        <v>-2.733542165256639</v>
       </c>
       <c r="G98">
-        <v>-5.406395929095383</v>
+        <v>-6.194861681568324</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.637596789359831</v>
       </c>
       <c r="E99">
-        <v>-37.23400321508515</v>
+        <v>-35.84697391838313</v>
       </c>
       <c r="F99">
-        <v>-2.258888471819924</v>
+        <v>-2.603535699959076</v>
       </c>
       <c r="G99">
-        <v>-4.99548300566629</v>
+        <v>-6.071814678244564</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.678080183501943</v>
       </c>
       <c r="E100">
-        <v>-39.99579114563</v>
+        <v>-37.57503377999514</v>
       </c>
       <c r="F100">
-        <v>-2.675571357673924</v>
+        <v>-2.589508954727472</v>
       </c>
       <c r="G100">
-        <v>-5.508387277291814</v>
+        <v>-5.684737852932335</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.705496186236654</v>
       </c>
       <c r="E101">
-        <v>-41.70203211154703</v>
+        <v>-40.59007207749406</v>
       </c>
       <c r="F101">
-        <v>-2.92620468416715</v>
+        <v>-2.707876858015701</v>
       </c>
       <c r="G101">
-        <v>-4.98277390099675</v>
+        <v>-6.645961796488424</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.704478143820987</v>
       </c>
       <c r="E102">
-        <v>-42.75907838546311</v>
+        <v>-43.07777297986816</v>
       </c>
       <c r="F102">
-        <v>-2.458381708333921</v>
+        <v>-2.356615944532599</v>
       </c>
       <c r="G102">
-        <v>-5.662032207223422</v>
+        <v>-6.584758111038956</v>
       </c>
     </row>
   </sheetData>
